--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487008_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487008_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.0484</v>
+        <v>11.5912</v>
       </c>
       <c r="E2" t="n">
-        <v>9.760199999999999</v>
+        <v>9.303100000000001</v>
       </c>
       <c r="F2" t="n">
         <v>2.2881</v>
@@ -610,10 +610,10 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9454</v>
+        <v>0.4882</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6856</v>
+        <v>0.2284</v>
       </c>
       <c r="U2" t="n">
         <v>0.2598</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4832</v>
+        <v>4.6834</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0264</v>
+        <v>2.1969</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4568</v>
+        <v>2.4865</v>
       </c>
       <c r="G3" t="n">
         <v>1.4088</v>
@@ -688,13 +688,13 @@
         <v>1.2321</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2746</v>
+        <v>-0.0745</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.527</v>
+        <v>-0.3565</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2523</v>
+        <v>0.282</v>
       </c>
       <c r="V3" t="n">
         <v>2.117</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0509</v>
+        <v>2.9406</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5125</v>
+        <v>1.7876</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5384</v>
+        <v>1.153</v>
       </c>
       <c r="G4" t="n">
         <v>1.3488</v>
@@ -766,13 +766,13 @@
         <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1074</v>
+        <v>-0.0028</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8563</v>
+        <v>-0.5813</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9638</v>
+        <v>0.5784</v>
       </c>
       <c r="V4" t="n">
         <v>-0.048</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MOLINA MARTINEZ</t>
+          <t>L. FERRANDO ORTELLS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6616</v>
+        <v>2.568</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3163</v>
+        <v>1.7309</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3453</v>
+        <v>0.8371</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8665</v>
+        <v>1.1045</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8715</v>
+        <v>0.5125</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.005</v>
+        <v>0.592</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0444</v>
+        <v>1.648</v>
       </c>
       <c r="K5" t="n">
-        <v>2.005</v>
+        <v>1.1748</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0395</v>
+        <v>0.4732</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1779</v>
+        <v>-0.5435</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1335</v>
+        <v>-0.6623</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0445</v>
+        <v>0.1188</v>
       </c>
       <c r="P5" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6427</v>
+        <v>2.4641</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4193</v>
+        <v>-0.3661</v>
       </c>
       <c r="T5" t="n">
-        <v>0.12</v>
+        <v>-0.4612</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2993</v>
+        <v>0.0951</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2402</v>
+        <v>1.4189</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1786</v>
+        <v>2.5975</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4189</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. FERRANDO ORTELLS</t>
+          <t>J. MOLINA MARTINEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2476</v>
+        <v>2.3199</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3512</v>
+        <v>2.2117</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8964</v>
+        <v>0.1082</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1045</v>
+        <v>1.8665</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5125</v>
+        <v>1.8715</v>
       </c>
       <c r="I6" t="n">
-        <v>0.592</v>
+        <v>-0.005</v>
       </c>
       <c r="J6" t="n">
-        <v>1.648</v>
+        <v>2.0444</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1748</v>
+        <v>2.005</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4732</v>
+        <v>0.0395</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5435</v>
+        <v>-0.1779</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6623</v>
+        <v>-0.1335</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1188</v>
+        <v>-0.0445</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4641</v>
+        <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6865</v>
+        <v>0.0776</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8409</v>
+        <v>0.0154</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1544</v>
+        <v>0.0622</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4189</v>
+        <v>-0.2402</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5975</v>
+        <v>1.1786</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1786</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2332</v>
+        <v>1.1599</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0108</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.244</v>
+        <v>1.0662</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4856</v>
@@ -1000,13 +1000,13 @@
         <v>1.0267</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0759</v>
+        <v>-0.1491</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3875</v>
+        <v>-0.2829</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3116</v>
+        <v>0.1338</v>
       </c>
       <c r="V7" t="n">
         <v>1.7679</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9977</v>
+        <v>0.8683</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2174</v>
+        <v>-0.4653</v>
       </c>
       <c r="F8" t="n">
-        <v>1.215</v>
+        <v>1.3336</v>
       </c>
       <c r="G8" t="n">
         <v>0.5288</v>
@@ -1078,13 +1078,13 @@
         <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0713</v>
+        <v>-0.058</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0272</v>
+        <v>-0.2752</v>
       </c>
       <c r="U8" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.2171</v>
       </c>
       <c r="V8" t="n">
         <v>0.1922</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3528</v>
+        <v>0.1139</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2162</v>
+        <v>-0.4254</v>
       </c>
       <c r="F9" t="n">
-        <v>0.569</v>
+        <v>0.5393</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4179</v>
@@ -1156,13 +1156,13 @@
         <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5304</v>
+        <v>0.2915</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3098</v>
+        <v>0.1006</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2205</v>
+        <v>0.1909</v>
       </c>
       <c r="V9" t="n">
         <v>0.2402</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3586</v>
+        <v>-2.0482</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9488</v>
+        <v>-3.0534</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5901999999999999</v>
+        <v>1.0052</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0893</v>
@@ -1234,13 +1234,13 @@
         <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4479</v>
+        <v>-0.1375</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2517</v>
+        <v>0.1471</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6996</v>
+        <v>-0.2846</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7848</v>
+        <v>-2.3228</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9341</v>
+        <v>-2.6203</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1493</v>
+        <v>0.2975</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5958</v>
@@ -1312,13 +1312,13 @@
         <v>0.4107</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5249</v>
+        <v>-0.0629</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4611</v>
+        <v>-0.1473</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0638</v>
+        <v>0.0844</v>
       </c>
       <c r="V11" t="n">
         <v>-0.048</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3538</v>
+        <v>-3.9667</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9786</v>
+        <v>-3.7694</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3751</v>
+        <v>-0.1973</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9792</v>
@@ -1390,13 +1390,13 @@
         <v>0.8214</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9159</v>
+        <v>-0.5288</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5928</v>
+        <v>-0.3836</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.323</v>
+        <v>-0.1452</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2267</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.5782</v>
+        <v>17.9075</v>
       </c>
       <c r="E13" t="n">
-        <v>6.660700000000002</v>
+        <v>6.990199999999999</v>
       </c>
       <c r="F13" t="n">
         <v>10.9174</v>
@@ -1459,7 +1459,7 @@
         <v>0.2529000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>3.08</v>
+        <v>3.080000000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-11.2937</v>
@@ -1468,10 +1468,10 @@
         <v>14.374</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8519000000000001</v>
+        <v>-0.5224000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.3257</v>
+        <v>-1.9965</v>
       </c>
       <c r="U13" t="n">
         <v>1.4739</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9833</v>
+        <v>2.312</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4637</v>
+        <v>0.9407</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5196</v>
+        <v>1.3714</v>
       </c>
       <c r="G14" t="n">
         <v>1.761</v>
@@ -1546,13 +1546,13 @@
         <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>1.017</v>
+        <v>0.3457</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3408</v>
+        <v>-0.1823</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6762</v>
+        <v>0.528</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. IKPEZE</t>
+          <t>N. RAKOCEVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1896</v>
+        <v>0.8168</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6748</v>
+        <v>1.8817</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4852</v>
+        <v>-1.0649</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1027</v>
+        <v>1.2015</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-1.1611</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1027</v>
+        <v>2.3626</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9388</v>
+        <v>1.7058</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8599</v>
+        <v>-0.6092</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0789</v>
+        <v>2.3151</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8362000000000001</v>
+        <v>-0.5044</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8599</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0238</v>
+        <v>0.0475</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0267</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4265</v>
+        <v>0.0794</v>
       </c>
       <c r="T15" t="n">
-        <v>0.736</v>
+        <v>-0.128</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6905</v>
+        <v>0.2074</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.3663</v>
+        <v>1.1786</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.3573</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.3663</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. RAKOCEVIC</t>
+          <t>A. HARO VAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.163</v>
+        <v>0.2683</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3587</v>
+        <v>0.5032</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5217</v>
+        <v>-0.2349</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2015</v>
+        <v>1.5772</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1611</v>
+        <v>-0.8693</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3626</v>
+        <v>2.4465</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7058</v>
+        <v>1.5735</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6092</v>
+        <v>0.8244</v>
       </c>
       <c r="L16" t="n">
-        <v>2.3151</v>
+        <v>0.7491</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5044</v>
+        <v>0.0037</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-1.6937</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0475</v>
+        <v>1.6974</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4107</v>
+        <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9004</v>
+        <v>0.0164</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.651</v>
+        <v>-0.3722</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2494</v>
+        <v>0.3885</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1786</v>
+        <v>-3.1733</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3573</v>
+        <v>-0.6982</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1786</v>
+        <v>-2.4751</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. HARO VAL</t>
+          <t>A. IKPEZE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6296</v>
+        <v>-0.5705</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1894</v>
+        <v>1.1518</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.819</v>
+        <v>-1.7223</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5772</v>
+        <v>0.1027</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8693</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4465</v>
+        <v>0.1027</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5735</v>
+        <v>0.9388</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8244</v>
+        <v>0.8599</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7491</v>
+        <v>0.0789</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0037</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6937</v>
+        <v>-0.8599</v>
       </c>
       <c r="O17" t="n">
-        <v>1.6974</v>
+        <v>0.0238</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8815</v>
+        <v>0.6663</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6860000000000001</v>
+        <v>0.213</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1956</v>
+        <v>0.4534</v>
       </c>
       <c r="V17" t="n">
-        <v>-3.1733</v>
+        <v>-2.3663</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4751</v>
+        <v>-2.3663</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1836</v>
+        <v>-0.7512</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5437</v>
+        <v>-1.2298</v>
       </c>
       <c r="F18" t="n">
-        <v>0.36</v>
+        <v>0.4786</v>
       </c>
       <c r="G18" t="n">
         <v>-1.7376</v>
@@ -1858,13 +1858,13 @@
         <v>1.0267</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5951</v>
+        <v>-0.1627</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7246</v>
+        <v>-0.4108</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1295</v>
+        <v>0.248</v>
       </c>
       <c r="V18" t="n">
         <v>0.1224</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2013</v>
+        <v>-2.067</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9962</v>
+        <v>-2.8915</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.8245</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1784</v>
@@ -1936,13 +1936,13 @@
         <v>0.8214</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1824</v>
+        <v>0.3167</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0931</v>
+        <v>0.0115</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2755</v>
+        <v>0.3052</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. FALL</t>
+          <t>A. LIBROIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6429</v>
+        <v>-2.7121</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0245</v>
+        <v>-2.1819</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6185</v>
+        <v>-0.5303</v>
       </c>
       <c r="G20" t="n">
-        <v>0.337</v>
+        <v>-3.8782</v>
       </c>
       <c r="H20" t="n">
-        <v>0.363</v>
+        <v>-2.6728</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0261</v>
+        <v>-1.2054</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8781</v>
+        <v>-2.3638</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7202</v>
+        <v>-1.4818</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1579</v>
+        <v>-0.882</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5411</v>
+        <v>-1.5144</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3572</v>
+        <v>-1.191</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1839</v>
+        <v>-0.3234</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.4641</v>
+        <v>1.2321</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.616</v>
+        <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>1.8415</v>
+        <v>-0.066</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1776</v>
+        <v>-0.2986</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6639</v>
+        <v>0.2326</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.3573</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. LIBROIA</t>
+          <t>M. FALL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4026</v>
+        <v>-4.0185</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4957</v>
+        <v>-2.1751</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9069</v>
+        <v>-1.8434</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.8782</v>
+        <v>0.337</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.6728</v>
+        <v>0.363</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2054</v>
+        <v>-0.0261</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.3638</v>
+        <v>0.8781</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4818</v>
+        <v>0.7202</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.882</v>
+        <v>0.1579</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5144</v>
+        <v>-0.5411</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.191</v>
+        <v>-0.3572</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3234</v>
+        <v>-0.1839</v>
       </c>
       <c r="P21" t="n">
-        <v>1.2321</v>
+        <v>-2.4641</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7564</v>
+        <v>0.4659</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6124000000000001</v>
+        <v>0.0269</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.144</v>
+        <v>0.4389</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
       <c r="W21" t="n">
-        <v>0.4805</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.4805</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1187</v>
+        <v>-4.3454</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2621</v>
+        <v>-2.4713</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8566</v>
+        <v>-1.8741</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2802</v>
@@ -2170,13 +2170,13 @@
         <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0926</v>
+        <v>0.8659</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4802</v>
+        <v>0.271</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.5949</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0563</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.4094</v>
+        <v>-5.1158</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1033</v>
+        <v>-3.2665</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.306</v>
+        <v>-1.8493</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1276</v>
@@ -2248,13 +2248,13 @@
         <v>1.8481</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5746</v>
+        <v>-0.281</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.4415</v>
+        <v>-0.6046</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1331</v>
+        <v>0.3237</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4751</v>
@@ -2281,25 +2281,25 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-17.5782</v>
+        <v>-16.1834</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.738900000000001</v>
+        <v>-9.738700000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.8394</v>
+        <v>-6.444699999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.222600000000001</v>
+        <v>-5.2226</v>
       </c>
       <c r="H24" t="n">
-        <v>-6.9584</v>
+        <v>-6.958399999999999</v>
       </c>
       <c r="I24" t="n">
         <v>1.7357</v>
       </c>
       <c r="J24" t="n">
-        <v>2.0701</v>
+        <v>2.070099999999999</v>
       </c>
       <c r="K24" t="n">
         <v>2.3229</v>
@@ -2326,13 +2326,13 @@
         <v>11.294</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8520000000000005</v>
+        <v>2.2466</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.474</v>
+        <v>-1.4741</v>
       </c>
       <c r="U24" t="n">
-        <v>2.3259</v>
+        <v>3.7206</v>
       </c>
       <c r="V24" t="n">
         <v>-10.1273</v>
